--- a/templates/_masters/PAM-003-commission-split-calculator-DEMO.xlsx
+++ b/templates/_masters/PAM-003-commission-split-calculator-DEMO.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -266,7 +266,7 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00888888"/>
+      <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
     <font>
@@ -280,12 +280,6 @@
       <b val="1"/>
       <color rgb="0012304E"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -498,7 +492,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00999999"/>
+        <color rgb="006B7280"/>
       </bottom>
     </border>
     <border>
@@ -713,16 +707,16 @@
     <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="44" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="43" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
